--- a/SGC-CKN/Excel/9d748b62-304c-4a7d-b872-e4a697e16c79_Thi_công_cọc_khoan_nhồi_TP-2_D1200_14-03-2025.xlsx
+++ b/SGC-CKN/Excel/9d748b62-304c-4a7d-b872-e4a697e16c79_Thi_công_cọc_khoan_nhồi_TP-2_D1200_14-03-2025.xlsx
@@ -35,7 +35,7 @@
     <t>Số hiệu cọc</t>
   </si>
   <si>
-    <t>TP-2</t>
+    <t>TP-02 (T8)</t>
   </si>
   <si>
     <t>Tên Máy khoan</t>

--- a/SGC-CKN/Excel/9d748b62-304c-4a7d-b872-e4a697e16c79_Thi_công_cọc_khoan_nhồi_TP-2_D1200_14-03-2025.xlsx
+++ b/SGC-CKN/Excel/9d748b62-304c-4a7d-b872-e4a697e16c79_Thi_công_cọc_khoan_nhồi_TP-2_D1200_14-03-2025.xlsx
@@ -53,13 +53,13 @@
     <t>Bắt đầu thi công</t>
   </si>
   <si>
-    <t>11:00 13/03/2025</t>
+    <t>11:00 13/03/2026</t>
   </si>
   <si>
     <t>Kết thúc thi công</t>
   </si>
   <si>
-    <t>10:15 14/03/2025</t>
+    <t>10:15 14/03/2026</t>
   </si>
   <si>
     <t>Địa chất TT</t>
@@ -99,30 +99,30 @@
   </si>
   <si>
     <t xml:space="preserve">11:00
-13/03/2025</t>
+13/03/2026</t>
   </si>
   <si>
     <t xml:space="preserve">11:15
-13/03/2025</t>
+13/03/2026</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
     <t xml:space="preserve">11:25
-13/03/2025</t>
+13/03/2026</t>
   </si>
   <si>
     <t xml:space="preserve">11:35
-13/03/2025</t>
+13/03/2026</t>
   </si>
   <si>
     <t xml:space="preserve">11:50
-13/03/2025</t>
+13/03/2026</t>
   </si>
   <si>
     <t xml:space="preserve">12:05
-13/03/2025</t>
+13/03/2026</t>
   </si>
   <si>
     <t>2</t>
@@ -132,7 +132,7 @@
   </si>
   <si>
     <t xml:space="preserve">12:15
-13/03/2025</t>
+13/03/2026</t>
   </si>
   <si>
     <t>3</t>
@@ -142,31 +142,31 @@
   </si>
   <si>
     <t xml:space="preserve">17:15
-13/03/2025</t>
+13/03/2026</t>
   </si>
   <si>
     <t xml:space="preserve">17:18
-13/03/2025</t>
+13/03/2026</t>
   </si>
   <si>
     <t xml:space="preserve">17:33
-13/03/2025</t>
+13/03/2026</t>
   </si>
   <si>
     <t xml:space="preserve">17:45
-13/03/2025</t>
+13/03/2026</t>
   </si>
   <si>
     <t xml:space="preserve">17:55
-13/03/2025</t>
+13/03/2026</t>
   </si>
   <si>
     <t xml:space="preserve">20:29
-13/03/2025</t>
+13/03/2026</t>
   </si>
   <si>
     <t xml:space="preserve">20:40
-13/03/2025</t>
+13/03/2026</t>
   </si>
   <si>
     <t>5</t>
@@ -176,83 +176,83 @@
   </si>
   <si>
     <t xml:space="preserve">20:59
-13/03/2025</t>
+13/03/2026</t>
   </si>
   <si>
     <t xml:space="preserve">21:10
-13/03/2025</t>
+13/03/2026</t>
   </si>
   <si>
     <t xml:space="preserve">21:20
-13/03/2025</t>
+13/03/2026</t>
   </si>
   <si>
     <t xml:space="preserve">22:02
-13/03/2025</t>
+13/03/2026</t>
   </si>
   <si>
     <t xml:space="preserve">22:14
-13/03/2025</t>
+13/03/2026</t>
   </si>
   <si>
     <t xml:space="preserve">22:30
-13/03/2025</t>
+13/03/2026</t>
   </si>
   <si>
     <t xml:space="preserve">01:18
-14/03/2025</t>
+13/03/2026</t>
   </si>
   <si>
     <t xml:space="preserve">01:25
-14/03/2025</t>
+13/03/2026</t>
   </si>
   <si>
     <t xml:space="preserve">01:35
-14/03/2025</t>
+13/03/2026</t>
   </si>
   <si>
     <t xml:space="preserve">01:50
-14/03/2025</t>
+13/03/2026</t>
   </si>
   <si>
     <t xml:space="preserve">02:08
-14/03/2025</t>
+13/03/2026</t>
   </si>
   <si>
     <t xml:space="preserve">03:35
-14/03/2025</t>
+13/03/2026</t>
   </si>
   <si>
     <t xml:space="preserve">03:55
-14/03/2025</t>
+13/03/2026</t>
   </si>
   <si>
     <t xml:space="preserve">04:08
-14/03/2025</t>
+13/03/2026</t>
   </si>
   <si>
     <t xml:space="preserve">04:20
-14/03/2025</t>
+13/03/2026</t>
   </si>
   <si>
     <t xml:space="preserve">04:50
-14/03/2025</t>
+13/03/2026</t>
   </si>
   <si>
     <t xml:space="preserve">07:32
-14/03/2025</t>
+13/03/2026</t>
   </si>
   <si>
     <t xml:space="preserve">07:42
-14/03/2025</t>
+13/03/2026</t>
   </si>
   <si>
     <t xml:space="preserve">08:23
-14/03/2025</t>
+13/03/2026</t>
   </si>
   <si>
     <t xml:space="preserve">08:45
-14/03/2025</t>
+13/03/2026</t>
   </si>
   <si>
     <t>6</t>
@@ -262,7 +262,7 @@
   </si>
   <si>
     <t xml:space="preserve">10:15
-14/03/2025</t>
+13/03/2026</t>
   </si>
   <si>
     <t>ẢNH BIÊN BẢN GỐC</t>

--- a/SGC-CKN/Excel/9d748b62-304c-4a7d-b872-e4a697e16c79_Thi_công_cọc_khoan_nhồi_TP-2_D1200_14-03-2025.xlsx
+++ b/SGC-CKN/Excel/9d748b62-304c-4a7d-b872-e4a697e16c79_Thi_công_cọc_khoan_nhồi_TP-2_D1200_14-03-2025.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="87">
   <si>
     <t>Dự án</t>
   </si>
@@ -35,7 +35,7 @@
     <t>Số hiệu cọc</t>
   </si>
   <si>
-    <t>TP-02 (T8)</t>
+    <t>8</t>
   </si>
   <si>
     <t>Tên Máy khoan</t>
@@ -95,7 +95,7 @@
     <t>1</t>
   </si>
   <si>
-    <t>Cát mịn lẫn bụi, vỏ sò, màu xám nâu, xám ghi, kết cấu xốp</t>
+    <t>Cát mịn lẫn bụi, lẫn vỏ sò, màu xám nâu, xám ghi, kết cấu xốp đến chặt vừa</t>
   </si>
   <si>
     <t xml:space="preserve">11:00
@@ -109,25 +109,34 @@
     <t/>
   </si>
   <si>
+    <t>2</t>
+  </si>
+  <si>
     <t xml:space="preserve">11:25
 13/03/2026</t>
   </si>
   <si>
+    <t>3</t>
+  </si>
+  <si>
     <t xml:space="preserve">11:35
 13/03/2026</t>
   </si>
   <si>
+    <t>4</t>
+  </si>
+  <si>
     <t xml:space="preserve">11:50
 13/03/2026</t>
   </si>
   <si>
+    <t>5</t>
+  </si>
+  <si>
     <t xml:space="preserve">12:05
 13/03/2026</t>
   </si>
   <si>
-    <t>2</t>
-  </si>
-  <si>
     <t>Cát pha - Sét pha màu xám ghi, xám xanh, đôi chỗ lẫn vỏ sò, hữu cơ (gỗ, lá, rễ cây...), trạng thái dẻo mềm đến dẻo chảy</t>
   </si>
   <si>
@@ -135,10 +144,7 @@
 13/03/2026</t>
   </si>
   <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>Sét pha màu xám ghi, xám vàng, trạng thái dẻo cứng đến nửa cứng</t>
+    <t>Sét pha, xám xanh, xám đen, xám ghi, xám vàng, nâu đỏ, TT dẻo cứng đến nửa cứng</t>
   </si>
   <si>
     <t xml:space="preserve">17:15
@@ -149,18 +155,30 @@
 13/03/2026</t>
   </si>
   <si>
+    <t>9</t>
+  </si>
+  <si>
     <t xml:space="preserve">17:33
 13/03/2026</t>
   </si>
   <si>
+    <t>10</t>
+  </si>
+  <si>
     <t xml:space="preserve">17:45
 13/03/2026</t>
   </si>
   <si>
+    <t>11</t>
+  </si>
+  <si>
     <t xml:space="preserve">17:55
 13/03/2026</t>
   </si>
   <si>
+    <t>12</t>
+  </si>
+  <si>
     <t xml:space="preserve">20:29
 13/03/2026</t>
   </si>
@@ -169,9 +187,6 @@
 13/03/2026</t>
   </si>
   <si>
-    <t>5</t>
-  </si>
-  <si>
     <t>Cát hạt mịn đến hạt vừa màu xám ghi, xám vàng, đôi chỗ kẹp sét pha, kết cấu chặt vừa đến chặt</t>
   </si>
   <si>
@@ -255,10 +270,10 @@
 13/03/2026</t>
   </si>
   <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>Cát mịn đến vừa, màu xám nâu, xám ghi, đôi chỗ lẫn sạn, kết cấu rất chặt</t>
+    <t>29</t>
+  </si>
+  <si>
+    <t>Cát mịn đến hạt vừa, màu xám ghi, xám vàng, đôi chỗ kẹp sét pha, kết cấu chặt vừa đến rất chặt</t>
   </si>
   <si>
     <t xml:space="preserve">10:15
@@ -1194,7 +1209,7 @@
     </row>
     <row r="12" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>11</v>
@@ -1206,7 +1221,7 @@
         <v>29</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F12" s="5">
         <v>1.2</v>
@@ -1229,7 +1244,7 @@
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>11</v>
@@ -1238,10 +1253,10 @@
         <v>27</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F13" s="5">
         <v>-0.85</v>
@@ -1264,7 +1279,7 @@
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>11</v>
@@ -1273,10 +1288,10 @@
         <v>27</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F14" s="5">
         <v>-2.85</v>
@@ -1299,7 +1314,7 @@
     </row>
     <row r="15" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>11</v>
@@ -1308,10 +1323,10 @@
         <v>27</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="F15" s="5">
         <v>-4.85</v>
@@ -1334,19 +1349,19 @@
     </row>
     <row r="16" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="9" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B16" s="9" t="s">
         <v>11</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F16" s="9">
         <v>-6.85</v>
@@ -1369,19 +1384,19 @@
     </row>
     <row r="17" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="9" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B17" s="9" t="s">
         <v>11</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F17" s="9">
         <v>-8.85</v>
@@ -1404,19 +1419,19 @@
     </row>
     <row r="18" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="13" t="s">
-        <v>38</v>
+        <v>7</v>
       </c>
       <c r="B18" s="13" t="s">
         <v>11</v>
       </c>
       <c r="C18" s="14" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D18" s="15" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E18" s="15" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F18" s="13">
         <v>-10.85</v>
@@ -1439,19 +1454,19 @@
     </row>
     <row r="19" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="13" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="B19" s="13" t="s">
         <v>11</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D19" s="15" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E19" s="15" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F19" s="13">
         <v>-12.85</v>
@@ -1474,19 +1489,19 @@
     </row>
     <row r="20" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="13" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="B20" s="13" t="s">
         <v>11</v>
       </c>
       <c r="C20" s="14" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D20" s="15" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="E20" s="15" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="F20" s="13">
         <v>-14.85</v>
@@ -1509,19 +1524,19 @@
     </row>
     <row r="21" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="13" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="B21" s="13" t="s">
         <v>11</v>
       </c>
       <c r="C21" s="14" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D21" s="15" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="E21" s="15" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F21" s="13">
         <v>-16.85</v>
@@ -1544,19 +1559,19 @@
     </row>
     <row r="22" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="13" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="B22" s="13" t="s">
         <v>11</v>
       </c>
       <c r="C22" s="14" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D22" s="15" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="E22" s="15" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="F22" s="13">
         <v>-18.85</v>
@@ -1579,19 +1594,19 @@
     </row>
     <row r="23" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="16" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="B23" s="16" t="s">
         <v>11</v>
       </c>
       <c r="C23" s="17" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="D23" s="18" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="E23" s="18" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="F23" s="16">
         <v>-20.85</v>
@@ -1614,19 +1629,19 @@
     </row>
     <row r="24" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="16" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="B24" s="16" t="s">
         <v>11</v>
       </c>
       <c r="C24" s="17" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="D24" s="18" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="E24" s="18" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="F24" s="16">
         <v>-22.85</v>
@@ -1649,19 +1664,19 @@
     </row>
     <row r="25" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="16" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="B25" s="16" t="s">
         <v>11</v>
       </c>
       <c r="C25" s="17" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="D25" s="18" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="E25" s="18" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="F25" s="16">
         <v>-24.85</v>
@@ -1684,19 +1699,19 @@
     </row>
     <row r="26" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="16" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="B26" s="16" t="s">
         <v>11</v>
       </c>
       <c r="C26" s="17" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="D26" s="18" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="E26" s="18" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="F26" s="16">
         <v>-26.85</v>
@@ -1719,19 +1734,19 @@
     </row>
     <row r="27" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" s="16" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="B27" s="16" t="s">
         <v>11</v>
       </c>
       <c r="C27" s="17" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="D27" s="18" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="E27" s="18" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="F27" s="16">
         <v>-28.85</v>
@@ -1754,19 +1769,19 @@
     </row>
     <row r="28" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" s="16" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="B28" s="16" t="s">
         <v>11</v>
       </c>
       <c r="C28" s="17" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="D28" s="18" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="E28" s="18" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="F28" s="16">
         <v>-30.85</v>
@@ -1789,19 +1804,19 @@
     </row>
     <row r="29" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" s="16" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="B29" s="16" t="s">
         <v>11</v>
       </c>
       <c r="C29" s="17" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="D29" s="18" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="E29" s="18" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="F29" s="16">
         <v>-32.849999999999994</v>
@@ -1824,19 +1839,19 @@
     </row>
     <row r="30" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" s="16" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="B30" s="16" t="s">
         <v>11</v>
       </c>
       <c r="C30" s="17" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="D30" s="18" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="E30" s="18" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="F30" s="16">
         <v>-34.849999999999994</v>
@@ -1859,19 +1874,19 @@
     </row>
     <row r="31" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" s="16" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="B31" s="16" t="s">
         <v>11</v>
       </c>
       <c r="C31" s="17" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="D31" s="18" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="E31" s="18" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="F31" s="16">
         <v>-36.849999999999994</v>
@@ -1894,19 +1909,19 @@
     </row>
     <row r="32" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" s="16" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="B32" s="16" t="s">
         <v>11</v>
       </c>
       <c r="C32" s="17" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="D32" s="18" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="E32" s="18" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="F32" s="16">
         <v>-38.849999999999994</v>
@@ -1929,19 +1944,19 @@
     </row>
     <row r="33" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" s="16" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="B33" s="16" t="s">
         <v>11</v>
       </c>
       <c r="C33" s="17" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="D33" s="18" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="E33" s="18" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="F33" s="16">
         <v>-40.849999999999994</v>
@@ -1964,19 +1979,19 @@
     </row>
     <row r="34" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" s="16" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="B34" s="16" t="s">
         <v>11</v>
       </c>
       <c r="C34" s="17" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="D34" s="18" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="E34" s="18" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="F34" s="16">
         <v>-42.849999999999994</v>
@@ -1999,19 +2014,19 @@
     </row>
     <row r="35" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" s="16" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="B35" s="16" t="s">
         <v>11</v>
       </c>
       <c r="C35" s="17" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="D35" s="18" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="E35" s="18" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="F35" s="16">
         <v>-44.849999999999994</v>
@@ -2034,19 +2049,19 @@
     </row>
     <row r="36" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" s="16" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="B36" s="16" t="s">
         <v>11</v>
       </c>
       <c r="C36" s="17" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="D36" s="18" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="E36" s="18" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="F36" s="16">
         <v>-46.849999999999994</v>
@@ -2069,19 +2084,19 @@
     </row>
     <row r="37" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" s="16" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="B37" s="16" t="s">
         <v>11</v>
       </c>
       <c r="C37" s="17" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="D37" s="18" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="E37" s="18" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="F37" s="16">
         <v>-48.849999999999994</v>
@@ -2104,19 +2119,19 @@
     </row>
     <row r="38" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" s="16" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="B38" s="16" t="s">
         <v>11</v>
       </c>
       <c r="C38" s="17" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="D38" s="18" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="E38" s="18" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="F38" s="16">
         <v>-50.05</v>
@@ -2139,19 +2154,19 @@
     </row>
     <row r="39" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" s="19" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="B39" s="19" t="s">
         <v>11</v>
       </c>
       <c r="C39" s="20" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="D39" s="21" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="E39" s="21" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="F39" s="19">
         <v>-53.05</v>
@@ -2174,7 +2189,7 @@
     </row>
     <row r="42" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" s="22" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="B42" s="22"/>
       <c r="C42" s="22"/>
@@ -2280,31 +2295,31 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -2344,7 +2359,7 @@
         <v>11</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D3" s="9">
         <v>2</v>
@@ -2373,7 +2388,7 @@
         <v>11</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D4" s="13">
         <v>5</v>
@@ -2402,7 +2417,7 @@
         <v>11</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="D5" s="16">
         <v>16</v>
@@ -2431,7 +2446,7 @@
         <v>11</v>
       </c>
       <c r="C6" s="20" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="D6" s="19">
         <v>1</v>
@@ -2454,7 +2469,7 @@
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="23" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="B7" s="24" t="s">
         <v>30</v>
